--- a/mosip_master/xlsx/zone_user_h.xlsx
+++ b/mosip_master/xlsx/zone_user_h.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahesh.Binayak\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d80e659244fef04f/Bureau/UGP/Dev-Système_intérimaire/master-data-customised/mosip-data-1.2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56EF1852-D84B-4180-83B4-1EDB24753668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{55DD0BF5-60EC-4CC6-84D9-7581F0C0DA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EBB18FC-C322-8946-B947-31B05BDC58CC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>lang_code</t>
   </si>
@@ -40,21 +40,6 @@
   </si>
   <si>
     <t>eff_dtimes</t>
-  </si>
-  <si>
-    <t>eng</t>
-  </si>
-  <si>
-    <t>MOR</t>
-  </si>
-  <si>
-    <t>globaladmin</t>
-  </si>
-  <si>
-    <t>now()</t>
-  </si>
-  <si>
-    <t>service-account-mosip-resident-client</t>
   </si>
 </sst>
 </file>
@@ -76,7 +61,7 @@
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -141,9 +126,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -181,7 +166,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -287,7 +272,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -429,7 +414,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -437,15 +422,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -462,39 +447,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
